--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UROS DE RIVAS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_UROS DE RIVAS.xlsx
@@ -565,13 +565,13 @@
         <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>48.2993</v>
+        <v>53.1446</v>
       </c>
       <c r="E2" t="n">
-        <v>38.3774</v>
+        <v>41.9886</v>
       </c>
       <c r="F2" t="n">
-        <v>9.9222</v>
+        <v>11.1561</v>
       </c>
       <c r="G2" t="n">
         <v>20.298</v>
@@ -610,13 +610,13 @@
         <v>44.6274</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1747999999999992</v>
+        <v>4.6706</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06679999999999969</v>
+        <v>3.6781</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2415999999999999</v>
+        <v>0.9925000000000002</v>
       </c>
       <c r="V2" t="n">
         <v>32.2512</v>
@@ -643,13 +643,13 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>45.8609</v>
+        <v>45.4321</v>
       </c>
       <c r="E3" t="n">
-        <v>31.6778</v>
+        <v>30.1023</v>
       </c>
       <c r="F3" t="n">
-        <v>14.1829</v>
+        <v>15.3296</v>
       </c>
       <c r="G3" t="n">
         <v>18.9043</v>
@@ -688,13 +688,13 @@
         <v>38.0304</v>
       </c>
       <c r="S3" t="n">
-        <v>9.327300000000001</v>
+        <v>8.8988</v>
       </c>
       <c r="T3" t="n">
-        <v>9.683199999999999</v>
+        <v>8.107699999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3557000000000001</v>
+        <v>0.7910999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>1.1359</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BIERSACK LOPEZ</t>
+          <t>O. MENDEZ BLANCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>44.54949999999999</v>
+        <v>42.2306</v>
       </c>
       <c r="E4" t="n">
-        <v>15.8854</v>
+        <v>38.7768</v>
       </c>
       <c r="F4" t="n">
-        <v>28.664</v>
+        <v>3.453999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>5.002299999999999</v>
+        <v>36.4209</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2892</v>
+        <v>18.0575</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2870999999999999</v>
+        <v>18.3633</v>
       </c>
       <c r="J4" t="n">
-        <v>19.786</v>
+        <v>44.89570000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>14.7559</v>
+        <v>22.9285</v>
       </c>
       <c r="L4" t="n">
-        <v>5.03</v>
+        <v>21.9673</v>
       </c>
       <c r="M4" t="n">
-        <v>-14.7838</v>
+        <v>-8.4749</v>
       </c>
       <c r="N4" t="n">
-        <v>-9.466699999999999</v>
+        <v>-4.8708</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.317299999999999</v>
+        <v>-3.6039</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9403</v>
+        <v>2.328399999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-43.0751</v>
+        <v>-20.5675</v>
       </c>
       <c r="R4" t="n">
-        <v>45.0153</v>
+        <v>22.8959</v>
       </c>
       <c r="S4" t="n">
-        <v>32.7439</v>
+        <v>-0.1901000000000002</v>
       </c>
       <c r="T4" t="n">
-        <v>20.3567</v>
+        <v>0.2350000000000002</v>
       </c>
       <c r="U4" t="n">
-        <v>12.387</v>
+        <v>-0.4254999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>4.8631</v>
+        <v>3.6716</v>
       </c>
       <c r="W4" t="n">
-        <v>18.8178</v>
+        <v>14.2133</v>
       </c>
       <c r="X4" t="n">
-        <v>-13.9545</v>
+        <v>-10.5418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. MENDEZ BLANCO</t>
+          <t>A. BIERSACK LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>36.9692</v>
+        <v>28.6157</v>
       </c>
       <c r="E5" t="n">
-        <v>34.3488</v>
+        <v>5.740700000000002</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6204</v>
+        <v>22.8746</v>
       </c>
       <c r="G5" t="n">
-        <v>36.4209</v>
+        <v>5.002299999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>18.0575</v>
+        <v>5.2892</v>
       </c>
       <c r="I5" t="n">
-        <v>18.3633</v>
+        <v>-0.2870999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>44.89570000000001</v>
+        <v>19.786</v>
       </c>
       <c r="K5" t="n">
-        <v>22.9285</v>
+        <v>14.7559</v>
       </c>
       <c r="L5" t="n">
-        <v>21.9673</v>
+        <v>5.03</v>
       </c>
       <c r="M5" t="n">
-        <v>-8.4749</v>
+        <v>-14.7838</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.8708</v>
+        <v>-9.466699999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.6039</v>
+        <v>-5.317299999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>2.328399999999999</v>
+        <v>1.9403</v>
       </c>
       <c r="Q5" t="n">
-        <v>-20.5675</v>
+        <v>-43.0751</v>
       </c>
       <c r="R5" t="n">
-        <v>22.8959</v>
+        <v>45.0153</v>
       </c>
       <c r="S5" t="n">
-        <v>-5.4516</v>
+        <v>16.8103</v>
       </c>
       <c r="T5" t="n">
-        <v>-4.193000000000001</v>
+        <v>10.2123</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.2589</v>
+        <v>6.5979</v>
       </c>
       <c r="V5" t="n">
-        <v>3.6716</v>
+        <v>4.8631</v>
       </c>
       <c r="W5" t="n">
-        <v>14.2133</v>
+        <v>18.8178</v>
       </c>
       <c r="X5" t="n">
-        <v>-10.5418</v>
+        <v>-13.9545</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. VILLAMANDOS TORRES</t>
+          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>22.4985</v>
+        <v>21.7024</v>
       </c>
       <c r="E6" t="n">
-        <v>9.876300000000001</v>
+        <v>12.31</v>
       </c>
       <c r="F6" t="n">
-        <v>12.6222</v>
+        <v>9.3926</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.095700000000001</v>
+        <v>10.161</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.9337</v>
+        <v>4.3308</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8375999999999997</v>
+        <v>5.830100000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>5.642</v>
+        <v>21.2063</v>
       </c>
       <c r="K6" t="n">
-        <v>2.784899999999999</v>
+        <v>13.7299</v>
       </c>
       <c r="L6" t="n">
-        <v>2.8569</v>
+        <v>7.4766</v>
       </c>
       <c r="M6" t="n">
-        <v>-11.7376</v>
+        <v>-11.0455</v>
       </c>
       <c r="N6" t="n">
-        <v>-9.718299999999999</v>
+        <v>-9.399000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0191</v>
+        <v>-1.6464</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1643</v>
+        <v>9.701699999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-28.3289</v>
+        <v>-16.2989</v>
       </c>
       <c r="R6" t="n">
-        <v>27.1645</v>
+        <v>26.0003</v>
       </c>
       <c r="S6" t="n">
-        <v>14.1225</v>
+        <v>3.0992</v>
       </c>
       <c r="T6" t="n">
-        <v>9.409599999999999</v>
+        <v>1.0961</v>
       </c>
       <c r="U6" t="n">
-        <v>4.712800000000001</v>
+        <v>2.0028</v>
       </c>
       <c r="V6" t="n">
-        <v>15.636</v>
+        <v>-1.2593</v>
       </c>
       <c r="W6" t="n">
-        <v>23.1535</v>
+        <v>6.306</v>
       </c>
       <c r="X6" t="n">
-        <v>-7.5176</v>
+        <v>-7.565300000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>M. VILLAMANDOS TORRES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>21.0786</v>
+        <v>17.7089</v>
       </c>
       <c r="E7" t="n">
-        <v>16.9512</v>
+        <v>6.6572</v>
       </c>
       <c r="F7" t="n">
-        <v>4.127699999999999</v>
+        <v>11.0517</v>
       </c>
       <c r="G7" t="n">
-        <v>-23.5569</v>
+        <v>-6.095700000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-9.3721</v>
+        <v>-6.9337</v>
       </c>
       <c r="I7" t="n">
-        <v>-14.1846</v>
+        <v>0.8375999999999997</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5770000000000002</v>
+        <v>5.642</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3589</v>
+        <v>2.784899999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-4.9358</v>
+        <v>2.8569</v>
       </c>
       <c r="M7" t="n">
-        <v>-22.9802</v>
+        <v>-11.7376</v>
       </c>
       <c r="N7" t="n">
-        <v>-13.7309</v>
+        <v>-9.718299999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.248900000000001</v>
+        <v>-2.0191</v>
       </c>
       <c r="P7" t="n">
-        <v>14.9403</v>
+        <v>-1.1643</v>
       </c>
       <c r="Q7" t="n">
-        <v>-29.6872</v>
+        <v>-28.3289</v>
       </c>
       <c r="R7" t="n">
-        <v>44.6275</v>
+        <v>27.1645</v>
       </c>
       <c r="S7" t="n">
-        <v>14.4931</v>
+        <v>9.333</v>
       </c>
       <c r="T7" t="n">
-        <v>11.8275</v>
+        <v>6.1905</v>
       </c>
       <c r="U7" t="n">
-        <v>2.6659</v>
+        <v>3.1425</v>
       </c>
       <c r="V7" t="n">
-        <v>15.2022</v>
+        <v>15.636</v>
       </c>
       <c r="W7" t="n">
-        <v>35.388</v>
+        <v>23.1535</v>
       </c>
       <c r="X7" t="n">
-        <v>-20.1859</v>
+        <v>-7.5176</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>16.9004</v>
+        <v>14.7273</v>
       </c>
       <c r="E8" t="n">
-        <v>9.644300000000001</v>
+        <v>-4.087600000000002</v>
       </c>
       <c r="F8" t="n">
-        <v>7.2564</v>
+        <v>18.8147</v>
       </c>
       <c r="G8" t="n">
-        <v>10.161</v>
+        <v>22.731</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3308</v>
+        <v>11.5878</v>
       </c>
       <c r="I8" t="n">
-        <v>5.830100000000001</v>
+        <v>11.1428</v>
       </c>
       <c r="J8" t="n">
-        <v>21.2063</v>
+        <v>37.889</v>
       </c>
       <c r="K8" t="n">
-        <v>13.7299</v>
+        <v>22.2404</v>
       </c>
       <c r="L8" t="n">
-        <v>7.4766</v>
+        <v>15.6484</v>
       </c>
       <c r="M8" t="n">
-        <v>-11.0455</v>
+        <v>-15.1582</v>
       </c>
       <c r="N8" t="n">
-        <v>-9.399000000000001</v>
+        <v>-10.653</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.6464</v>
+        <v>-4.505100000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>9.701699999999999</v>
+        <v>-13.1942</v>
       </c>
       <c r="Q8" t="n">
-        <v>-16.2989</v>
+        <v>-55.8813</v>
       </c>
       <c r="R8" t="n">
-        <v>26.0003</v>
+        <v>42.6871</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.7027</v>
+        <v>4.9736</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5695</v>
+        <v>2.2824</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1335000000000001</v>
+        <v>2.6913</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2593</v>
+        <v>0.2172000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>6.306</v>
+        <v>11.6223</v>
       </c>
       <c r="X8" t="n">
-        <v>-7.565300000000001</v>
+        <v>-11.4052</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>10.7336</v>
+        <v>14.2951</v>
       </c>
       <c r="E9" t="n">
-        <v>8.168800000000001</v>
+        <v>9.3094</v>
       </c>
       <c r="F9" t="n">
-        <v>2.565</v>
+        <v>4.9857</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1642</v>
+        <v>-23.5569</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.6925</v>
+        <v>-9.3721</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5283</v>
+        <v>-14.1846</v>
       </c>
       <c r="J9" t="n">
-        <v>8.6995</v>
+        <v>-0.5770000000000002</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4884</v>
+        <v>4.3589</v>
       </c>
       <c r="L9" t="n">
-        <v>6.2114</v>
+        <v>-4.9358</v>
       </c>
       <c r="M9" t="n">
-        <v>-10.8639</v>
+        <v>-22.9802</v>
       </c>
       <c r="N9" t="n">
-        <v>-6.1808</v>
+        <v>-13.7309</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.6828</v>
+        <v>-9.248900000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>7.9557</v>
+        <v>14.9403</v>
       </c>
       <c r="Q9" t="n">
-        <v>-27.3587</v>
+        <v>-29.6872</v>
       </c>
       <c r="R9" t="n">
-        <v>35.3142</v>
+        <v>44.6275</v>
       </c>
       <c r="S9" t="n">
-        <v>22.5127</v>
+        <v>7.7094</v>
       </c>
       <c r="T9" t="n">
-        <v>18.1264</v>
+        <v>4.1854</v>
       </c>
       <c r="U9" t="n">
-        <v>4.3864</v>
+        <v>3.5239</v>
       </c>
       <c r="V9" t="n">
-        <v>-17.5699</v>
+        <v>15.2022</v>
       </c>
       <c r="W9" t="n">
-        <v>8.7014</v>
+        <v>35.388</v>
       </c>
       <c r="X9" t="n">
-        <v>-26.2714</v>
+        <v>-20.1859</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>9.485100000000001</v>
+        <v>9.5002</v>
       </c>
       <c r="E10" t="n">
-        <v>7.153799999999999</v>
+        <v>6.9536</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3315</v>
+        <v>2.5468</v>
       </c>
       <c r="G10" t="n">
         <v>2.4826</v>
@@ -1234,13 +1234,13 @@
         <v>7.1792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2842</v>
+        <v>-0.2692</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6717</v>
+        <v>0.4714999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9560000000000002</v>
+        <v>-0.7407000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>1.2717</v>
@@ -1267,13 +1267,13 @@
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>7.8408</v>
+        <v>8.4641</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6849</v>
+        <v>0.5163000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>8.5259</v>
+        <v>7.9478</v>
       </c>
       <c r="G11" t="n">
         <v>4.5506</v>
@@ -1312,13 +1312,13 @@
         <v>6.5971</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9918</v>
+        <v>2.6149</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5900000000000001</v>
+        <v>0.6111999999999997</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5818</v>
+        <v>2.0037</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2238</v>
@@ -1345,13 +1345,13 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>4.759</v>
+        <v>6.5809</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6199</v>
+        <v>-0.3976999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>6.379</v>
+        <v>6.9786</v>
       </c>
       <c r="G12" t="n">
         <v>4.1439</v>
@@ -1390,13 +1390,13 @@
         <v>8.9255</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4553</v>
+        <v>0.3665000000000003</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9903000000000001</v>
+        <v>0.2318</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.465</v>
+        <v>0.1347</v>
       </c>
       <c r="V12" t="n">
         <v>-2.0041</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. ROLDAN DE LA PORTILLA</t>
+          <t>D. MAGANTO LUCAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>4.083299999999999</v>
+        <v>5.157100000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4663000000000006</v>
+        <v>4.516999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>3.616999999999999</v>
+        <v>0.6403000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>9.361499999999999</v>
+        <v>3.1244</v>
       </c>
       <c r="H13" t="n">
-        <v>4.318700000000001</v>
+        <v>2.8356</v>
       </c>
       <c r="I13" t="n">
-        <v>5.0427</v>
+        <v>0.2886999999999995</v>
       </c>
       <c r="J13" t="n">
-        <v>11.0414</v>
+        <v>10.0324</v>
       </c>
       <c r="K13" t="n">
-        <v>8.3955</v>
+        <v>4.6384</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6464</v>
+        <v>5.394</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.68</v>
+        <v>-6.9081</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.0767</v>
+        <v>-1.8028</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3967</v>
+        <v>-5.1053</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.358</v>
+        <v>1.1641</v>
       </c>
       <c r="Q13" t="n">
-        <v>-16.8809</v>
+        <v>-9.313599999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>15.5228</v>
+        <v>10.4778</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3042</v>
+        <v>2.422299999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4248999999999999</v>
+        <v>1.7279</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.729</v>
+        <v>0.6943000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.616</v>
+        <v>-1.5537</v>
       </c>
       <c r="W13" t="n">
-        <v>5.8807</v>
+        <v>2.0702</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.4968</v>
+        <v>-3.6239</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. PEREZ CONTI</t>
+          <t>A. ROLDAN DE LA PORTILLA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7862</v>
+        <v>4.879200000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.2577</v>
+        <v>0.2895000000000003</v>
       </c>
       <c r="F14" t="n">
-        <v>8.043800000000001</v>
+        <v>4.5895</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.2355</v>
+        <v>9.361499999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.1159</v>
+        <v>4.318700000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8802999999999996</v>
+        <v>5.0427</v>
       </c>
       <c r="J14" t="n">
-        <v>9.8963</v>
+        <v>11.0414</v>
       </c>
       <c r="K14" t="n">
-        <v>7.0525</v>
+        <v>8.3955</v>
       </c>
       <c r="L14" t="n">
-        <v>2.8437</v>
+        <v>2.6464</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.1317</v>
+        <v>-1.68</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.1684</v>
+        <v>-4.0767</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9632</v>
+        <v>2.3967</v>
       </c>
       <c r="P14" t="n">
-        <v>5.821</v>
+        <v>-1.358</v>
       </c>
       <c r="Q14" t="n">
-        <v>-20.3734</v>
+        <v>-16.8809</v>
       </c>
       <c r="R14" t="n">
-        <v>26.1943</v>
+        <v>15.5228</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7361000000000003</v>
+        <v>-0.5081</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9507999999999999</v>
+        <v>0.2481999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2146999999999999</v>
+        <v>-0.7563</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5355</v>
+        <v>-2.616</v>
       </c>
       <c r="W14" t="n">
-        <v>5.2686</v>
+        <v>5.8807</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.804</v>
+        <v>-8.4968</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. MAGANTO LUCAS</t>
+          <t>A. PEREZ CONTI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2444</v>
+        <v>4.179600000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9313</v>
+        <v>-4.455299999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3132</v>
+        <v>8.6351</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1244</v>
+        <v>-2.2355</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8356</v>
+        <v>-3.1159</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2886999999999995</v>
+        <v>0.8802999999999996</v>
       </c>
       <c r="J15" t="n">
-        <v>10.0324</v>
+        <v>9.8963</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6384</v>
+        <v>7.0525</v>
       </c>
       <c r="L15" t="n">
-        <v>5.394</v>
+        <v>2.8437</v>
       </c>
       <c r="M15" t="n">
-        <v>-6.9081</v>
+        <v>-12.1317</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8028</v>
+        <v>-10.1684</v>
       </c>
       <c r="O15" t="n">
-        <v>-5.1053</v>
+        <v>-1.9632</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1641</v>
+        <v>5.821</v>
       </c>
       <c r="Q15" t="n">
-        <v>-9.313599999999999</v>
+        <v>-20.3734</v>
       </c>
       <c r="R15" t="n">
-        <v>10.4778</v>
+        <v>26.1943</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5096000000000003</v>
+        <v>1.1298</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1423000000000001</v>
+        <v>0.7530999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3672</v>
+        <v>0.3766</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.5537</v>
+        <v>-0.5355</v>
       </c>
       <c r="W15" t="n">
-        <v>2.0702</v>
+        <v>5.2686</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.6239</v>
+        <v>-5.804</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. VILA DE MIGUEL</t>
+          <t>S. PARADELA PARIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>2.071</v>
+        <v>1.4081</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4068</v>
+        <v>-2.220299999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3358</v>
+        <v>3.6284</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0416</v>
+        <v>-1.0174</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0537</v>
+        <v>0.1631999999999997</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01220000000000004</v>
+        <v>-1.1805</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1547000000000001</v>
+        <v>2.8419</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3170999999999999</v>
+        <v>2.5375</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1624</v>
+        <v>0.3043</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8866999999999998</v>
+        <v>-3.8593</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7365999999999998</v>
+        <v>-2.3743</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1502</v>
+        <v>-1.4848</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5523</v>
+        <v>2.5224</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-8.343599999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5523</v>
+        <v>10.8658</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3483</v>
+        <v>1.1089</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3377</v>
+        <v>0.03479999999999994</v>
       </c>
       <c r="U16" t="n">
-        <v>0.01060000000000001</v>
+        <v>1.0739</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.7881</v>
+        <v>-1.2057</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2239</v>
+        <v>3.2463</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.0119</v>
+        <v>-4.4519</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>1.081100000000001</v>
+        <v>0.6853999999999996</v>
       </c>
       <c r="E17" t="n">
-        <v>-15.2433</v>
+        <v>-1.3963</v>
       </c>
       <c r="F17" t="n">
-        <v>16.3239</v>
+        <v>2.082</v>
       </c>
       <c r="G17" t="n">
-        <v>22.731</v>
+        <v>-2.1642</v>
       </c>
       <c r="H17" t="n">
-        <v>11.5878</v>
+        <v>-3.6925</v>
       </c>
       <c r="I17" t="n">
-        <v>11.1428</v>
+        <v>1.5283</v>
       </c>
       <c r="J17" t="n">
-        <v>37.889</v>
+        <v>8.6995</v>
       </c>
       <c r="K17" t="n">
-        <v>22.2404</v>
+        <v>2.4884</v>
       </c>
       <c r="L17" t="n">
-        <v>15.6484</v>
+        <v>6.2114</v>
       </c>
       <c r="M17" t="n">
-        <v>-15.1582</v>
+        <v>-10.8639</v>
       </c>
       <c r="N17" t="n">
-        <v>-10.653</v>
+        <v>-6.1808</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.505100000000001</v>
+        <v>-4.6828</v>
       </c>
       <c r="P17" t="n">
-        <v>-13.1942</v>
+        <v>7.9557</v>
       </c>
       <c r="Q17" t="n">
-        <v>-55.8813</v>
+        <v>-27.3587</v>
       </c>
       <c r="R17" t="n">
-        <v>42.6871</v>
+        <v>35.3142</v>
       </c>
       <c r="S17" t="n">
-        <v>-8.6724</v>
+        <v>12.4646</v>
       </c>
       <c r="T17" t="n">
-        <v>-8.8734</v>
+        <v>8.561299999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2006000000000001</v>
+        <v>3.9035</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2172000000000001</v>
+        <v>-17.5699</v>
       </c>
       <c r="W17" t="n">
-        <v>11.6223</v>
+        <v>8.7014</v>
       </c>
       <c r="X17" t="n">
-        <v>-11.4052</v>
+        <v>-26.2714</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. PARADELA PARIS</t>
+          <t>C. VILA DE MIGUEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5336</v>
+        <v>0.6241</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.0256</v>
+        <v>2.9054</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4922</v>
+        <v>-2.2813</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0174</v>
+        <v>-1.0416</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1631999999999997</v>
+        <v>-1.0537</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1805</v>
+        <v>0.01220000000000004</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8419</v>
+        <v>-0.1547000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5375</v>
+        <v>-0.3170999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3043</v>
+        <v>0.1624</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.8593</v>
+        <v>-0.8866999999999998</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.3743</v>
+        <v>-0.7365999999999998</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4848</v>
+        <v>-0.1502</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5224</v>
+        <v>1.5523</v>
       </c>
       <c r="Q18" t="n">
-        <v>-8.343599999999999</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>10.8658</v>
+        <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.8324</v>
+        <v>1.9014</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.7706</v>
+        <v>1.8362</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.06220000000000023</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2057</v>
+        <v>-1.7881</v>
       </c>
       <c r="W18" t="n">
-        <v>3.2463</v>
+        <v>1.2239</v>
       </c>
       <c r="X18" t="n">
-        <v>-4.4519</v>
+        <v>-3.0119</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-19.3388</v>
+        <v>-0.7507999999999981</v>
       </c>
       <c r="E19" t="n">
-        <v>-14.7085</v>
+        <v>-1.287399999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.630399999999999</v>
+        <v>0.5371999999999997</v>
       </c>
       <c r="G19" t="n">
         <v>-15.8823</v>
@@ -1936,13 +1936,13 @@
         <v>44.2397</v>
       </c>
       <c r="S19" t="n">
-        <v>-17.9205</v>
+        <v>0.6674</v>
       </c>
       <c r="T19" t="n">
-        <v>-13.0949</v>
+        <v>0.3261000000000002</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.8256</v>
+        <v>0.3410999999999996</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0585</v>
@@ -1969,22 +1969,22 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>261.3685</v>
+        <v>278.5846</v>
       </c>
       <c r="E20" t="n">
-        <v>138.3483</v>
+        <v>146.2222</v>
       </c>
       <c r="F20" t="n">
-        <v>123.0211</v>
+        <v>132.3634</v>
       </c>
       <c r="G20" t="n">
         <v>85.18690000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>20.70389999999999</v>
+        <v>20.7039</v>
       </c>
       <c r="I20" t="n">
-        <v>64.482</v>
+        <v>64.48200000000001</v>
       </c>
       <c r="J20" t="n">
         <v>264.5103</v>
@@ -2008,22 +2008,22 @@
         <v>72.7628</v>
       </c>
       <c r="Q20" t="n">
-        <v>-385.1558999999999</v>
+        <v>-385.1559</v>
       </c>
       <c r="R20" t="n">
         <v>457.9171</v>
       </c>
       <c r="S20" t="n">
-        <v>59.9872</v>
+        <v>77.2033</v>
       </c>
       <c r="T20" t="n">
-        <v>42.91589999999999</v>
+        <v>50.7896</v>
       </c>
       <c r="U20" t="n">
-        <v>17.0701</v>
+        <v>26.4124</v>
       </c>
       <c r="V20" t="n">
-        <v>43.43430000000001</v>
+        <v>43.4343</v>
       </c>
       <c r="W20" t="n">
         <v>216.0759</v>
